--- a/Documents/Product Catalog/Home/Dressing Stool.xlsx
+++ b/Documents/Product Catalog/Home/Dressing Stool.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADB5A60-E150-46D6-8813-B20B16005CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3677A90-781C-4ABD-B37D-2FFA74ADE153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Home Furniture Specifications</t>
   </si>
@@ -195,12 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">  Talukder Furniture Ltd.</t>
-  </si>
-  <si>
-    <t>ড্রেসিং স্টুল</t>
-  </si>
-  <si>
-    <t>পদ্ম ড্রেসিং স্টুল</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
@@ -1526,7 +1520,7 @@
         <v>25</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
@@ -1606,7 +1600,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
